--- a/tabla_apilamiento.xlsx
+++ b/tabla_apilamiento.xlsx
@@ -26,16 +26,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -45,11 +43,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,12 +75,12 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -455,15 +448,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>DUNS Proveedor</t>
@@ -496,17 +492,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>111000001</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>EMB-11</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -526,17 +522,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>222000002</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>EMB-02</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -556,17 +552,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>222000002</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>EMB-14</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -586,17 +582,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>333000003</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>EMB-06</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -616,17 +612,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>444000004</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>EMB-17</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -646,17 +642,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>555000005</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>EMB-05</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -676,17 +672,17 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>555000005</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>EMB-19</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -706,17 +702,17 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>666000006</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>EMB-21</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -736,17 +732,17 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>888000008</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>EMB-08</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -766,17 +762,17 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>999000009</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>EMB-09</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -796,18 +792,138 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>101000010</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>EMB-25</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="2" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>777000007</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>EMB-50_6</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>222000002</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>EMB-30_6</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>112000011</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>EMB-30_6</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>667000016</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>EMB-30_6</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>889000018</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>EMB-30_6</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>666000006</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>EMB-40_8</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>101000010</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>EMB-40_8</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>112000011</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>EMB-40_8</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
